--- a/diseases/d132/2026-2029.xlsx
+++ b/diseases/d132/2026-2029.xlsx
@@ -10757,6 +10757,154 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>D132</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>vancomycin-resistant-staphylococcus-aureus-infection</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Vancomycin-resistant Staphylococcus aureus infection</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>D132</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Vancomycin-resistant Staphylococcus aureus infection</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>万古霉素耐药金黄色葡萄球菌感染</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP70" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr"/>
+      <c r="AT70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV70" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA70" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB70" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC70" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10790,7 +10938,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -10873,7 +11021,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10">
@@ -10883,7 +11031,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d132/2026-2029.xlsx
+++ b/diseases/d132/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -2245,9 +2242,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -3577,9 +3571,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -4909,9 +4900,6 @@
       <c r="O30" t="n">
         <v>1</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.001937969923792046</v>
       </c>
@@ -6241,9 +6229,6 @@
       <c r="O39" t="n">
         <v>1</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.001937969923792046</v>
       </c>
@@ -7869,9 +7854,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -8017,9 +7999,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -8165,9 +8144,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -8313,9 +8289,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -8461,9 +8434,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -8609,9 +8579,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -8757,9 +8724,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -8905,9 +8869,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -9053,9 +9014,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -9201,9 +9159,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -9349,9 +9304,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -9497,9 +9449,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -9645,9 +9594,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -9793,9 +9739,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -9941,9 +9884,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -10089,9 +10029,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -10237,9 +10174,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -10385,9 +10319,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -10533,9 +10464,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -10681,9 +10609,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -10827,9 +10752,6 @@
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" t="n">
         <v>0</v>
       </c>
       <c r="R70" t="n">

--- a/diseases/d132/2026-2029.xlsx
+++ b/diseases/d132/2026-2029.xlsx
@@ -10827,6 +10827,151 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>D132</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>vancomycin-resistant-staphylococcus-aureus-infection</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Vancomycin-resistant Staphylococcus aureus infection</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>D132</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Vancomycin-resistant Staphylococcus aureus infection</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>万古霉素耐药金黄色葡萄球菌感染</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP71" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr"/>
+      <c r="AT71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV71" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA71" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB71" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC71" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10860,7 +11005,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -10943,7 +11088,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -10953,7 +11098,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d132/2026-2029.xlsx
+++ b/diseases/d132/2026-2029.xlsx
@@ -10972,6 +10972,151 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>D132</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>vancomycin-resistant-staphylococcus-aureus-infection</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Vancomycin-resistant Staphylococcus aureus infection</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>D132</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Vancomycin-resistant Staphylococcus aureus infection</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>万古霉素耐药金黄色葡萄球菌感染</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP72" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr"/>
+      <c r="AT72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV72" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA72" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB72" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC72" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11005,7 +11150,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11233,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -11098,7 +11243,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d132/2026-2029.xlsx
+++ b/diseases/d132/2026-2029.xlsx
@@ -11117,6 +11117,296 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>D132</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>vancomycin-resistant-staphylococcus-aureus-infection</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Vancomycin-resistant Staphylococcus aureus infection</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>D132</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Vancomycin-resistant Staphylococcus aureus infection</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>万古霉素耐药金黄色葡萄球菌感染</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP73" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr"/>
+      <c r="AT73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV73" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA73" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC73" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>D132</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>vancomycin-resistant-staphylococcus-aureus-infection</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Vancomycin-resistant Staphylococcus aureus infection</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>D132</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Vancomycin-resistant Staphylococcus aureus infection</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>万古霉素耐药金黄色葡萄球菌感染</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP74" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr"/>
+      <c r="AT74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV74" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA74" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC74" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11150,7 +11440,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -11233,7 +11523,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10">
@@ -11243,7 +11533,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">
